--- a/Q6. Charts.xlsx
+++ b/Q6. Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\ExcleR\Excel Assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E896BBB-96ED-4D69-90C7-1BDCE72F2C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B827BB6A-3F00-416D-A525-08C3F6EDEEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>Create Line Chart with Proper formatting</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>%</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
   <si>
     <t>Note - Do not use Pivot Table or Pivot charts</t>
@@ -317,13 +314,26 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16426159230096238"/>
+          <c:y val="0.17171296296296298"/>
+          <c:w val="0.79079855643044616"/>
+          <c:h val="0.51681284631087776"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue'000</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -337,6 +347,336 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.1222222222222248E-2"/>
+                  <c:y val="4.4016112569262175E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.4555555555555559E-2"/>
+                  <c:y val="-9.4872776319626761E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.0111111111111113E-2"/>
+                  <c:y val="-7.172462817147858E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.4444444444444957E-3"/>
+                  <c:y val="-0.12728018372703412"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.7888888888888938E-2"/>
+                  <c:y val="7.6423519976669588E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.1222222222222275E-2"/>
+                  <c:y val="4.4016112569262175E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.0111111111111113E-2"/>
+                  <c:y val="-8.0983887430737825E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.9555555555555551E-2"/>
+                  <c:y val="5.7905001458151063E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.4555555555555557E-2"/>
+                  <c:y val="-7.1724628171478566E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.0111111111111113E-2"/>
+                  <c:y val="4.4016112569262175E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.7888888888888883E-2"/>
+                  <c:y val="-8.5613517060367447E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.1777777777777775E-2"/>
+                  <c:y val="-9.9502405949256342E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.3444444444444547E-2"/>
+                  <c:y val="-9.487277631962672E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.1222222222222324E-2"/>
+                  <c:y val="6.7164260717410412E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.5355424321959856E-2"/>
+                  <c:y val="-8.5613517060367447E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-9F1B-413F-93C7-40C3100CE60F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -394,7 +734,7 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:val>
+          <c:cat>
             <c:numRef>
               <c:f>Charts1!$C$7:$C$21</c:f>
               <c:numCache>
@@ -447,87 +787,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3A36-49C0-90F6-BAABDB05B21A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Charts1!$D$7:$D$21</c:f>
@@ -585,7 +845,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3A36-49C0-90F6-BAABDB05B21A}"/>
+              <c16:uniqueId val="{00000000-3A36-49C0-90F6-BAABDB05B21A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -609,6 +869,62 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" b="1"/>
+                  <a:t>DATE</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -650,6 +966,7 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:tickLblSkip val="2"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
@@ -659,21 +976,63 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Revenue'000</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-IN" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-IN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="&quot;₹&quot;#,##0_);[Red]\(&quot;₹&quot;#,##0\)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -831,7 +1190,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>COMBO CHART</a:t>
             </a:r>
           </a:p>
@@ -998,9 +1357,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Charts2!$C$7:$C$25</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2005</c:v>
@@ -1056,11 +1416,8 @@
                 <c:pt idx="17">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1122,254 +1479,12 @@
                 <c:pt idx="17">
                   <c:v>3490</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>77390</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-060D-4812-920C-FF12559AE190}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Charts2!$E$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Running Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Charts2!$C$7:$C$25</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>2005</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2006</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2007</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2008</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2009</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2010</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2011</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2012</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2013</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2014</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Charts2!$E$7:$E$25</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="1">
-                  <c:v>5078</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>13267</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20259</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>22431</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>26815</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>35524</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>39142</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>45514</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>48970</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>56448</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>61097</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>66928</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>68527</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>72222</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>73900</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>77390</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-060D-4812-920C-FF12559AE190}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1389,23 +1504,15 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Charts2!$F$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>%</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1476,9 +1583,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Charts2!$C$7:$C$25</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2005</c:v>
@@ -1534,18 +1642,15 @@
                 <c:pt idx="17">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Charts2!$F$7:$F$25</c:f>
+              <c:f>Charts2!$F$7:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="1">
                   <c:v>6.5615712624370076E-2</c:v>
                 </c:pt>
@@ -1603,13 +1708,13 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-060D-4812-920C-FF12559AE190}"/>
+              <c16:uniqueId val="{00000001-060D-4812-920C-FF12559AE190}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1617,8 +1722,8 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="902030176"/>
-        <c:axId val="902031136"/>
+        <c:axId val="434505728"/>
+        <c:axId val="434505248"/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="684395856"/>
@@ -1627,6 +1732,59 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1677,24 +1835,63 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Revenue'000</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-        </c:majorGridlines>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="none"/>
         <c:spPr>
           <a:noFill/>
           <a:ln>
@@ -1726,14 +1923,14 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="902031136"/>
+        <c:axId val="434505248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1762,23 +1959,22 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="902030176"/>
+        <c:crossAx val="434505728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="902030176"/>
+        <c:axId val="434505728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
-        <c:axPos val="t"/>
+        <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="902031136"/>
-        <c:crosses val="max"/>
+        <c:crossAx val="434505248"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2960,10 +3156,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>192405</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>49530</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>573405</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4572000" cy="1809750"/>
     <xdr:pic>
@@ -2985,7 +3181,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7530465" y="224790"/>
+          <a:off x="9100185" y="1299210"/>
           <a:ext cx="4572000" cy="1809750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2998,16 +3194,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>156210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3080,13 +3276,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>541020</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>60959</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>568817</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>32197</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3333,7 +3529,7 @@
     </row>
     <row r="4" spans="3:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="3:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4475,7 +4671,7 @@
     </row>
     <row r="4" spans="3:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="3:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4776,13 +4972,8 @@
       </c>
     </row>
     <row r="25" spans="3:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="16">
-        <f>SUM(D7:D24)</f>
-        <v>77390</v>
-      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" spans="3:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="3:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
